--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportContentEnum001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportContentEnum001.xlsx
@@ -1,28 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2715" windowWidth="10995" windowHeight="6135"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19290" windowHeight="6960"/>
   </bookViews>
   <sheets>
     <sheet name="sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>生效日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>指标值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>制作人</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -35,16 +28,28 @@
     <t>适用范围说明</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>年度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>指标类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报表文本值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="0.00000_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +173,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -215,7 +223,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -247,9 +255,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -281,6 +290,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -456,307 +466,332 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="16.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="29.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="27.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="28.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="21.375" style="18" customWidth="1"/>
-    <col min="7" max="7" width="22.5" style="18" customWidth="1"/>
-    <col min="8" max="8" width="22.625" style="18" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="6" customWidth="1"/>
-    <col min="10" max="10" width="16.5" style="6" customWidth="1"/>
+    <col min="2" max="3" width="29.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="27.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="28.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="21.375" style="18" customWidth="1"/>
+    <col min="8" max="8" width="22.5" style="18" customWidth="1"/>
+    <col min="9" max="9" width="22.625" style="18" customWidth="1"/>
+    <col min="10" max="10" width="15.125" style="6" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="7" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
-      <c r="F1" s="13"/>
+      <c r="F1" s="8" t="s">
+        <v>1</v>
+      </c>
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
-      <c r="I1" s="9"/>
+      <c r="I1" s="13"/>
       <c r="J1" s="9"/>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="9"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="3"/>
+      <c r="D2" s="1"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="15"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="14"/>
       <c r="H2" s="15"/>
-      <c r="I2" s="5"/>
+      <c r="I2" s="15"/>
       <c r="J2" s="5"/>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="D3" s="10"/>
       <c r="E3" s="11"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="12"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="14"/>
       <c r="J3" s="12"/>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="1"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="15"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
-      <c r="I4" s="5"/>
+      <c r="I4" s="15"/>
       <c r="J4" s="5"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="3"/>
+      <c r="D5" s="1"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="15"/>
+      <c r="F5" s="3"/>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
-      <c r="I5" s="5"/>
+      <c r="I5" s="15"/>
       <c r="J5" s="5"/>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="1"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="15"/>
+      <c r="F6" s="3"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
-      <c r="I6" s="5"/>
+      <c r="I6" s="15"/>
       <c r="J6" s="5"/>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
+      <c r="D7" s="1"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="15"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="15"/>
       <c r="J7" s="5"/>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="1"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="15"/>
+      <c r="F8" s="3"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="5"/>
+      <c r="I8" s="15"/>
       <c r="J8" s="5"/>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="3"/>
+      <c r="D9" s="1"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="15"/>
+      <c r="F9" s="3"/>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
-      <c r="I9" s="5"/>
+      <c r="I9" s="15"/>
       <c r="J9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
+      <c r="D10" s="1"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="15"/>
+      <c r="F10" s="3"/>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
-      <c r="I10" s="5"/>
+      <c r="I10" s="15"/>
       <c r="J10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="3"/>
+      <c r="D11" s="1"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="15"/>
+      <c r="F11" s="3"/>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
-      <c r="I11" s="5"/>
+      <c r="I11" s="15"/>
       <c r="J11" s="5"/>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="3"/>
+      <c r="D12" s="1"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="15"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
-      <c r="I12" s="5"/>
+      <c r="I12" s="15"/>
       <c r="J12" s="5"/>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="3"/>
+      <c r="D13" s="1"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="15"/>
+      <c r="F13" s="3"/>
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
-      <c r="I13" s="5"/>
+      <c r="I13" s="15"/>
       <c r="J13" s="5"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="3"/>
+      <c r="D14" s="1"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="15"/>
+      <c r="F14" s="3"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
-      <c r="I14" s="5"/>
+      <c r="I14" s="15"/>
       <c r="J14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-      <c r="D15" s="3"/>
+      <c r="D15" s="1"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="15"/>
+      <c r="F15" s="3"/>
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
-      <c r="I15" s="5"/>
+      <c r="I15" s="15"/>
       <c r="J15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="D16" s="3"/>
+      <c r="D16" s="1"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="15"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
-      <c r="I16" s="5"/>
+      <c r="I16" s="15"/>
       <c r="J16" s="5"/>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="3"/>
+      <c r="D17" s="1"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="15"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
-      <c r="I17" s="5"/>
+      <c r="I17" s="15"/>
       <c r="J17" s="5"/>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="3"/>
+      <c r="D18" s="1"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="15"/>
+      <c r="F18" s="3"/>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
-      <c r="I18" s="5"/>
+      <c r="I18" s="15"/>
       <c r="J18" s="5"/>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="3"/>
+      <c r="D19" s="1"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="15"/>
+      <c r="F19" s="3"/>
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
-      <c r="I19" s="5"/>
+      <c r="I19" s="15"/>
       <c r="J19" s="5"/>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="3"/>
+      <c r="D20" s="1"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="15"/>
+      <c r="F20" s="3"/>
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
-      <c r="I20" s="5"/>
+      <c r="I20" s="15"/>
       <c r="J20" s="5"/>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="3"/>
+      <c r="D21" s="1"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="15"/>
+      <c r="F21" s="3"/>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="5"/>
+      <c r="I21" s="15"/>
       <c r="J21" s="5"/>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="3"/>
+      <c r="D22" s="1"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="15"/>
+      <c r="F22" s="3"/>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
-      <c r="I22" s="5"/>
+      <c r="I22" s="15"/>
       <c r="J22" s="5"/>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="3"/>
+      <c r="D23" s="1"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="15"/>
+      <c r="F23" s="3"/>
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
-      <c r="I23" s="5"/>
+      <c r="I23" s="15"/>
       <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
